--- a/data/trans_camb/P45C_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R2-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,12</t>
+          <t>-0,37; 5,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 0,1</t>
+          <t>-4,85; 0,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 9,79</t>
+          <t>3,09; 9,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,07</t>
+          <t>0,78; 5,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 1,86</t>
+          <t>-2,52; 1,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,52</t>
+          <t>0,59; 4,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,26</t>
+          <t>1,02; 4,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,36</t>
+          <t>-2,85; 0,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,81</t>
+          <t>2,0; 5,83</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 64,58</t>
+          <t>-3,69; 64,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,01; 1,59</t>
+          <t>-48,6; 4,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,27; 124,91</t>
+          <t>29,75; 120,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,17; 90,84</t>
+          <t>9,45; 88,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,69; 30,94</t>
+          <t>-33,82; 28,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 79,4</t>
+          <t>5,63; 79,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,53; 62,71</t>
+          <t>11,56; 62,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,61; 5,59</t>
+          <t>-35,1; 6,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,76; 83,29</t>
+          <t>22,38; 81,1</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,43</t>
+          <t>-1,9; 3,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,97; -0,88</t>
+          <t>-6,22; -0,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 0,4</t>
+          <t>-8,14; 0,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,22</t>
+          <t>-1,87; 3,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 3,26</t>
+          <t>-1,6; 3,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 0,45</t>
+          <t>-6,05; 0,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,71</t>
+          <t>-1,19; 2,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,15</t>
+          <t>-3,15; 0,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,01; -0,32</t>
+          <t>-5,92; -0,4</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 19,56</t>
+          <t>-9,33; 18,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,18; -4,82</t>
+          <t>-30,15; -5,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,2; 1,95</t>
+          <t>-40,11; 0,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 24,0</t>
+          <t>-11,09; 24,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 23,77</t>
+          <t>-9,56; 23,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,89; 3,12</t>
+          <t>-38,15; 3,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 16,77</t>
+          <t>-6,64; 15,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 0,98</t>
+          <t>-17,54; 1,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,97; -2,03</t>
+          <t>-33,09; -2,72</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 9,59</t>
+          <t>-1,14; 9,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 2,34</t>
+          <t>-7,38; 2,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 0,1</t>
+          <t>-8,4; 0,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 1,57</t>
+          <t>-8,8; 1,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 4,2</t>
+          <t>-5,7; 4,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,37; -0,49</t>
+          <t>-9,74; -0,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 3,92</t>
+          <t>-3,16; 4,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 1,87</t>
+          <t>-4,83; 1,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,9; -1,73</t>
+          <t>-7,89; -1,73</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 58,51</t>
+          <t>-5,9; 60,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,22; 15,73</t>
+          <t>-35,46; 14,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-41,37; 0,88</t>
+          <t>-42,54; 1,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,41; 10,52</t>
+          <t>-39,9; 9,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 25,24</t>
+          <t>-27,34; 25,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,06; -3,03</t>
+          <t>-44,36; -3,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 22,88</t>
+          <t>-15,83; 24,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 10,61</t>
+          <t>-24,01; 11,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-38,37; -10,13</t>
+          <t>-39,5; -10,46</t>
         </is>
       </c>
     </row>
@@ -1325,42 +1325,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 3,86</t>
+          <t>-0,17; 3,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,87; -0,38</t>
+          <t>-3,91; -0,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,85</t>
+          <t>-3,9; 1,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,68</t>
+          <t>-0,66; 2,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,73</t>
+          <t>-0,48; 2,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,46</t>
+          <t>-2,76; 1,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,63</t>
+          <t>0,19; 2,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,72</t>
+          <t>-1,65; 0,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,47; 25,56</t>
+          <t>-0,85; 25,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,23; -2,66</t>
+          <t>-23,45; -2,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,96; 12,13</t>
+          <t>-24,42; 11,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 22,34</t>
+          <t>-4,77; 22,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 23,68</t>
+          <t>-3,67; 21,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,55; 12,14</t>
+          <t>-20,42; 14,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 19,32</t>
+          <t>1,3; 20,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 5,44</t>
+          <t>-11,29; 5,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 9,74</t>
+          <t>-15,05; 9,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P45C_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R2-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,99</t>
+          <t>5,38</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,48</t>
+          <t>2,39</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>3,56</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 5,02</t>
+          <t>-0,36; 4,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 0,31</t>
+          <t>-4,95; 0,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 9,71</t>
+          <t>2,01; 8,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,13</t>
+          <t>0,88; 5,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,64</t>
+          <t>-2,16; 1,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,73</t>
+          <t>0,32; 4,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,37</t>
+          <t>1,04; 4,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,47</t>
+          <t>-2,81; 0,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,83</t>
+          <t>1,6; 5,33</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>46,13%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 64,82</t>
+          <t>-4,09; 63,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-48,6; 4,14</t>
+          <t>-47,98; 2,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,75; 120,52</t>
+          <t>19,05; 110,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,45; 88,27</t>
+          <t>10,67; 89,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,82; 28,19</t>
+          <t>-28,98; 33,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 79,72</t>
+          <t>3,38; 82,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,56; 62,62</t>
+          <t>12,59; 61,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,1; 6,03</t>
+          <t>-33,93; 6,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,38; 81,1</t>
+          <t>18,82; 74,79</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,0</t>
+          <t>-0,62</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,24</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,67</t>
+          <t>-0,57</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 3,35</t>
+          <t>-1,91; 3,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,22; -0,92</t>
+          <t>-6,03; -1,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 0,12</t>
+          <t>-3,72; 2,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 3,36</t>
+          <t>-1,86; 3,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 3,17</t>
+          <t>-1,73; 3,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 0,54</t>
+          <t>-2,69; 1,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,52</t>
+          <t>-0,95; 2,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 0,25</t>
+          <t>-3,35; 0,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,92; -0,4</t>
+          <t>-2,42; 1,24</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-15,81%</t>
+          <t>-3,26%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-14,73%</t>
+          <t>-2,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-15,54%</t>
+          <t>-3,34%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 18,85</t>
+          <t>-9,55; 18,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,15; -5,08</t>
+          <t>-30,0; -5,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,11; 0,85</t>
+          <t>-18,08; 11,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 24,07</t>
+          <t>-11,4; 22,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 23,04</t>
+          <t>-10,38; 23,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,15; 3,34</t>
+          <t>-16,33; 14,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 15,15</t>
+          <t>-5,03; 16,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 1,49</t>
+          <t>-18,52; 2,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,09; -2,72</t>
+          <t>-13,52; 7,7</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-4,24</t>
+          <t>-3,15</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,22</t>
+          <t>-5,05</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,71</t>
+          <t>-4,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 9,39</t>
+          <t>-0,97; 9,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 2,37</t>
+          <t>-7,22; 2,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 0,26</t>
+          <t>-7,53; 1,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 1,4</t>
+          <t>-8,68; 1,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 4,2</t>
+          <t>-6,16; 3,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,74; -0,57</t>
+          <t>-9,62; -1,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 4,18</t>
+          <t>-3,45; 3,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 1,9</t>
+          <t>-4,75; 1,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -1,73</t>
+          <t>-7,01; -0,96</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-23,39%</t>
+          <t>-17,39%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-27,65%</t>
+          <t>-26,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-25,46%</t>
+          <t>-22,08%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 60,94</t>
+          <t>-4,95; 60,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,46; 14,45</t>
+          <t>-35,26; 13,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-42,54; 1,61</t>
+          <t>-37,17; 8,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,9; 9,24</t>
+          <t>-40,88; 8,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 25,55</t>
+          <t>-28,45; 23,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,36; -3,77</t>
+          <t>-44,51; -7,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 24,32</t>
+          <t>-17,06; 21,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,01; 11,26</t>
+          <t>-23,66; 9,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-39,5; -10,46</t>
+          <t>-35,5; -5,95</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>1,09</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,75</t>
+          <t>0,03; 3,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,91; -0,43</t>
+          <t>-4,13; -0,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 1,77</t>
+          <t>-0,61; 3,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,54</t>
+          <t>-0,57; 2,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,54</t>
+          <t>-0,53; 2,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 1,79</t>
+          <t>-0,65; 2,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,72</t>
+          <t>0,27; 2,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,73</t>
+          <t>-1,77; 0,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,3</t>
+          <t>-0,22; 2,41</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-1,67%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-0,82%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-1,44%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 25,34</t>
+          <t>0,04; 25,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,45; -2,83</t>
+          <t>-24,51; -3,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 11,77</t>
+          <t>-3,73; 21,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 22,06</t>
+          <t>-4,48; 21,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 21,95</t>
+          <t>-3,94; 24,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,42; 14,86</t>
+          <t>-4,86; 20,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,3; 20,35</t>
+          <t>1,76; 19,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 5,44</t>
+          <t>-12,11; 4,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 9,46</t>
+          <t>-1,4; 18,16</t>
         </is>
       </c>
     </row>
